--- a/docs/ISTAR (versión final). Requerimientos y Casos de Usos GammaLab 2.0 (1).xlsx
+++ b/docs/ISTAR (versión final). Requerimientos y Casos de Usos GammaLab 2.0 (1).xlsx
@@ -1555,7 +1555,7 @@
     <t>R70</t>
   </si>
   <si>
-    <t>El sistema debe ejecutar toda operación de cómputo pesada a través de un servicio de tareas registrado en el núcleo, que gestione la cola, la cancelación y la notificación de progreso.</t>
+    <t>El sistema debe ejecutar toda operación de cómputo pesada a través de un servicio de tareas registrado en el núcleo, que gestione la cola, la cancelación y la notificación de progreso. Se considera pesada toda operación que, con los datos típicos del laboratorio (una señal de hasta 1,8 millones de muestras por canal y hasta 60 trials de 30 501 muestras), pueda tardar más de 1 segundo en el hardware de referencia; R71 enumera además las operaciones que se despachan siempre por el servicio, sin importar su duración.</t>
   </si>
   <si>
     <t>8a. Si el actor no tiene permisos de escritura en la carpeta seleccionada o el disco está lleno, el sistema informa la causa con un mensaje del nivel de severidad correspondiente (R02) y conserva el estado del proyecto sin alterarlo.</t>
